--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:50</t>
+    <t xml:space="preserve">2026-09-09 22:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:38</t>
+    <t xml:space="preserve">2026-09-18 10:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:00</t>
+    <t xml:space="preserve">2026-09-23 12:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:06</t>
+    <t xml:space="preserve">2026-10-02 13:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:08</t>
+    <t xml:space="preserve">2026-10-04 08:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:21</t>
+    <t xml:space="preserve">2026-10-05 08:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
